--- a/Metrics/SFM_Calibration_narrow_door.xlsx
+++ b/Metrics/SFM_Calibration_narrow_door.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Piotr\CrowdEvacuation\Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8EA7BD-8AD7-4475-AF59-1AFCE8834C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404CDEE4-D025-42F0-8DFA-AB14C47A85F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E00F018A-51B7-4FBE-B871-94FC33AFF981}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -122,9 +122,6 @@
     <t>LC_001_SFM</t>
   </si>
   <si>
-    <t>---</t>
-  </si>
-  <si>
     <t>Mean headway [m]</t>
   </si>
   <si>
@@ -149,69 +146,6 @@
     <t>LC_001_SFM_cal_20</t>
   </si>
   <si>
-    <t>kanoniczny (inne r)</t>
-  </si>
-  <si>
-    <t>duzy nacisk na sciane, odpychanie do tylu</t>
-  </si>
-  <si>
-    <t>większe odpychnie do tyłu do połowy symulacji, następnie stabilizacja i ewakuacja w ścisku</t>
-  </si>
-  <si>
-    <t>trzymanie większych odstępow przez agentów z tylu, brak agresji i przepychania, duże odstępy pod koniec ewakuacji i zwolnienie powodujące zablokowanie</t>
-  </si>
-  <si>
-    <t>mocny ścisk, odpychanie w lewo i prawo w 1/4 ewakuacji, sprawna ewakuacja</t>
-  </si>
-  <si>
-    <t>znowu to samo wystrzeliwywanie na boki czasami podczas ewakuacji, większe spowolnienie pod koniec</t>
-  </si>
-  <si>
-    <t>na początku podczas ewakuacji kilka odepchań do tyłu</t>
-  </si>
-  <si>
-    <t>szybsza ewakuacja, niewiele oscylacji, odepchań, duży ścisk</t>
-  </si>
-  <si>
-    <t>brak nienaturalnego opdychania do tyłu jak w poprzednich symulacjach</t>
-  </si>
-  <si>
-    <t>brak nienaturalnego opdychania do tyłu jak w poprzednich symulacjach, duże odstępy z tyłu, zablokowanie na koniec</t>
-  </si>
-  <si>
-    <t>brak nienaturalnych oscylacji, sprawna ewakuacja</t>
-  </si>
-  <si>
-    <t>duże odstępy między agentami, bardzo powolna ewakuacja, brak oscylacji</t>
-  </si>
-  <si>
-    <t>dobra gęstość, sprawne interakcje, spowolnienie na koniec</t>
-  </si>
-  <si>
-    <t>mało odpychania do tyłu, dobra gęstość</t>
-  </si>
-  <si>
-    <t>spowolnienie pod koniec mimo szybkiej ewakuacji na początku, problemy z zablokowaniem pod koniec</t>
-  </si>
-  <si>
-    <t>duża gęstość, brak nienaturalnego odpychania tłumu, najlepiej wyglądająca symulacja do tej pory</t>
-  </si>
-  <si>
-    <t>to samo co w cal_15</t>
-  </si>
-  <si>
-    <t>to samo co w cal_15, większe odstępy</t>
-  </si>
-  <si>
-    <t>to samo co w cal_15 ale mniejszy scisk pod koniec</t>
-  </si>
-  <si>
-    <t>to samo co w cal_15 ale mniejszy scisk pod koniec, problemy z wyjściem przez drzwi pod koniec</t>
-  </si>
-  <si>
-    <t>to samo co w cal_15 ale mniejszy scisk i rownowaga pod koniec umozliwiajaca zakonczenie</t>
-  </si>
-  <si>
     <t>LC_001_SFM_cal_21</t>
   </si>
   <si>
@@ -224,16 +158,7 @@
     <t>Fine tuning:</t>
   </si>
   <si>
-    <t>duza gestosc, brak nienaturalnych artefaktow, sprawna ewakuacja</t>
-  </si>
-  <si>
-    <t>bardzo duzy scisk przy wyjsciu, brak artefaktow</t>
-  </si>
-  <si>
-    <t>zwolnienie pod koniec, lekki problem z potencjalnym blokowaniem wyjścia ostatnich agentów</t>
-  </si>
-  <si>
-    <t>Stałe:  m=80kg, r=0.2m, v₀=N(1.34,0.26) m/s</t>
+    <t>Stałe:  m=80kg, r=N(0.23,0.01) m, v₀=N(1.34,0.26) m/s</t>
   </si>
 </sst>
 </file>
@@ -307,7 +232,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,14 +259,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -384,7 +303,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -437,6 +356,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -444,9 +366,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -454,9 +373,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -811,55 +727,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
+      <c r="A2" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
+      <c r="A3" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -872,10 +788,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>3</v>
@@ -890,7 +806,7 @@
         <v>6</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>7</v>
@@ -922,29 +838,27 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="5">
-        <v>76.92</v>
+        <v>69.5</v>
       </c>
       <c r="H6" s="5">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="I6" s="5">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="J6" s="7">
         <v>0.47</v>
       </c>
       <c r="K6" s="6">
         <f>0.3*ABS(G6-36.3)/36.3 + 0.25*ABS(H6-2.56)/2.56 + 0.2*ABS(I6-0.25)/0.25 + 0.25*ABS(J6-0.34)/0.34</f>
-        <v>0.57112665213296065</v>
+        <v>0.49710902558337383</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M6" s="15"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -963,30 +877,20 @@
       <c r="F7" s="14">
         <v>0.3</v>
       </c>
-      <c r="G7" s="8">
-        <v>38.64</v>
-      </c>
-      <c r="H7" s="8">
-        <v>2.41</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0.44</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0.35</v>
-      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
       <c r="K7" s="9">
         <f t="shared" ref="K7:K26" si="0">0.3*ABS(G7-36.3)/36.3 + 0.25*ABS(H7-2.56)/2.56 + 0.2*ABS(I7-0.25)/0.25 + 0.25*ABS(J7-0.34)/0.34</f>
-        <v>0.19334022165167722</v>
+        <v>1</v>
       </c>
       <c r="L7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M7" s="16"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -1005,30 +909,20 @@
       <c r="F8" s="14">
         <v>0.5</v>
       </c>
-      <c r="G8" s="8">
-        <v>42.38</v>
-      </c>
-      <c r="H8" s="8">
-        <v>2.19</v>
-      </c>
-      <c r="I8" s="8">
-        <v>0.41</v>
-      </c>
-      <c r="J8" s="8">
-        <v>0.37</v>
-      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
       <c r="K8" s="9">
         <f t="shared" si="0"/>
-        <v>0.23643956991370929</v>
+        <v>1</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>4</v>
       </c>
@@ -1047,30 +941,20 @@
       <c r="F9" s="14">
         <v>0.5</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="9" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="M9" s="16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>5</v>
       </c>
@@ -1089,30 +973,20 @@
       <c r="F10" s="14">
         <v>0.3</v>
       </c>
-      <c r="G10" s="8">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="H10" s="8">
-        <v>2.57</v>
-      </c>
-      <c r="I10" s="8">
-        <v>0.39</v>
-      </c>
-      <c r="J10" s="8">
-        <v>0.37</v>
-      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
       <c r="K10" s="9">
         <f t="shared" si="0"/>
-        <v>0.13586183231040344</v>
+        <v>1</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M10" s="16"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>6</v>
       </c>
@@ -1131,30 +1005,20 @@
       <c r="F11" s="14">
         <v>0.5</v>
       </c>
-      <c r="G11" s="8">
-        <v>47.94</v>
-      </c>
-      <c r="H11" s="8">
-        <v>1.94</v>
-      </c>
-      <c r="I11" s="8">
-        <v>0.34</v>
-      </c>
-      <c r="J11" s="8">
-        <v>0.4</v>
-      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
       <c r="K11" s="9">
         <f t="shared" si="0"/>
-        <v>0.27286286916626157</v>
+        <v>1</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="M11" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M11" s="16"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>7</v>
       </c>
@@ -1173,30 +1037,20 @@
       <c r="F12" s="14">
         <v>0.3</v>
       </c>
-      <c r="G12" s="8">
-        <v>47.5</v>
-      </c>
-      <c r="H12" s="8">
-        <v>1.96</v>
-      </c>
-      <c r="I12" s="8">
-        <v>0.3</v>
-      </c>
-      <c r="J12" s="8">
-        <v>0.42</v>
-      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
       <c r="K12" s="9">
         <f t="shared" si="0"/>
-        <v>0.24997926288283906</v>
+        <v>1</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M12" s="16"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>8</v>
       </c>
@@ -1215,30 +1069,20 @@
       <c r="F13" s="14">
         <v>0.3</v>
       </c>
-      <c r="G13" s="8">
-        <v>38.74</v>
-      </c>
-      <c r="H13" s="8">
-        <v>2.4</v>
-      </c>
-      <c r="I13" s="8">
-        <v>0.35</v>
-      </c>
-      <c r="J13" s="8">
-        <v>0.4</v>
-      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
       <c r="K13" s="9">
         <f t="shared" si="0"/>
-        <v>0.15990793631502193</v>
+        <v>1</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M13" s="16"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>9</v>
       </c>
@@ -1257,30 +1101,20 @@
       <c r="F14" s="14">
         <v>0.5</v>
       </c>
-      <c r="G14" s="8">
-        <v>61.54</v>
-      </c>
-      <c r="H14" s="8">
-        <v>1.51</v>
-      </c>
-      <c r="I14" s="8">
-        <v>0.27</v>
-      </c>
-      <c r="J14" s="8">
-        <v>0.43</v>
-      </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
       <c r="K14" s="9">
         <f t="shared" si="0"/>
-        <v>0.3933105744105494</v>
+        <v>1</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="M14" s="16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M14" s="16"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>10</v>
       </c>
@@ -1299,30 +1133,20 @@
       <c r="F15" s="14">
         <v>0.5</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="9" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="M15" s="16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M15" s="16"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>11</v>
       </c>
@@ -1341,30 +1165,20 @@
       <c r="F16" s="14">
         <v>0.3</v>
       </c>
-      <c r="G16" s="8">
-        <v>55.16</v>
-      </c>
-      <c r="H16" s="8">
-        <v>1.69</v>
-      </c>
-      <c r="I16" s="8">
-        <v>0.31</v>
-      </c>
-      <c r="J16" s="8">
-        <v>0.44</v>
-      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
       <c r="K16" s="9">
         <f t="shared" si="0"/>
-        <v>0.36235811785974714</v>
+        <v>1</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M16" s="16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M16" s="16"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>12</v>
       </c>
@@ -1383,30 +1197,20 @@
       <c r="F17" s="14">
         <v>0.5</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K17" s="9" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="L17" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="M17" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M17" s="16"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>13</v>
       </c>
@@ -1425,28 +1229,18 @@
       <c r="F18" s="14">
         <v>0.3</v>
       </c>
-      <c r="G18" s="3">
-        <v>59.66</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1.59</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0.27</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0.47</v>
-      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
       <c r="K18" s="9">
         <f t="shared" si="0"/>
-        <v>0.39937264903378705</v>
+        <v>1</v>
       </c>
       <c r="L18" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M18" s="17" t="s">
-        <v>49</v>
-      </c>
+      <c r="M18" s="17"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
@@ -1467,30 +1261,20 @@
       <c r="F19" s="14">
         <v>0.3</v>
       </c>
-      <c r="G19" s="3">
-        <v>42.62</v>
-      </c>
-      <c r="H19" s="3">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0.34</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0.42</v>
-      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
       <c r="K19" s="9">
         <f t="shared" si="0"/>
-        <v>0.22016430937044235</v>
+        <v>1</v>
       </c>
       <c r="L19" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="M19" s="17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M19" s="17"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>15</v>
       </c>
@@ -1509,70 +1293,50 @@
       <c r="F20" s="14">
         <v>0.3</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K20" s="9" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="L20" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M20" s="17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="18">
+      <c r="M20" s="17"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="19">
         <v>16</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <v>800</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <v>0.08</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <v>60000</v>
       </c>
-      <c r="E21" s="19">
-        <v>120000</v>
-      </c>
-      <c r="F21" s="19">
+      <c r="E21" s="20">
+        <v>120000</v>
+      </c>
+      <c r="F21" s="20">
         <v>0.3</v>
       </c>
-      <c r="G21" s="20">
-        <v>35.74</v>
-      </c>
-      <c r="H21" s="20">
-        <v>2.6</v>
-      </c>
-      <c r="I21" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="J21" s="20">
-        <v>0.38</v>
-      </c>
-      <c r="K21" s="21">
-        <f t="shared" si="0"/>
-        <v>0.10194611387943603</v>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="L21" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="M21" s="23" t="s">
-        <v>52</v>
-      </c>
+      <c r="M21" s="23"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
@@ -1593,28 +1357,18 @@
       <c r="F22" s="14">
         <v>0.3</v>
       </c>
-      <c r="G22" s="3">
-        <v>37.42</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0.4</v>
-      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
       <c r="K22" s="9">
         <f t="shared" si="0"/>
-        <v>0.124209782905931</v>
+        <v>1</v>
       </c>
       <c r="L22" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="M22" s="17" t="s">
-        <v>53</v>
-      </c>
+      <c r="M22" s="17"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
@@ -1635,30 +1389,20 @@
       <c r="F23" s="14">
         <v>0.3</v>
       </c>
-      <c r="G23" s="3">
-        <v>41.56</v>
-      </c>
-      <c r="H23" s="3">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0.32</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0.42</v>
-      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
       <c r="K23" s="9">
         <f t="shared" si="0"/>
-        <v>0.18954460379193</v>
+        <v>1</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="M23" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="M23" s="17"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>19</v>
       </c>
@@ -1677,30 +1421,20 @@
       <c r="F24" s="14">
         <v>0.3</v>
       </c>
-      <c r="G24" s="3">
-        <v>47.94</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1.94</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0.32</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0.44</v>
-      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
       <c r="K24" s="9">
         <f t="shared" si="0"/>
-        <v>0.28627463387214386</v>
+        <v>1</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M24" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="M24" s="17"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>20</v>
       </c>
@@ -1719,30 +1453,20 @@
       <c r="F25" s="14">
         <v>0.3</v>
       </c>
-      <c r="G25" s="3">
-        <v>56.28</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1.65</v>
-      </c>
-      <c r="I25" s="3">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0.46</v>
-      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
       <c r="K25" s="9">
         <f t="shared" si="0"/>
-        <v>0.36622644855979591</v>
+        <v>1</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M25" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="M25" s="17"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>21</v>
       </c>
@@ -1761,171 +1485,101 @@
       <c r="F26" s="14">
         <v>0.3</v>
       </c>
-      <c r="G26" s="3">
-        <v>57.22</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1.63</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0.27</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0.47</v>
-      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
       <c r="K26" s="9">
         <f t="shared" si="0"/>
-        <v>0.37530110977758874</v>
+        <v>1</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M26" s="17" t="s">
-        <v>57</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="M26" s="17"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="24"/>
-    </row>
-    <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>22</v>
       </c>
-      <c r="B32" s="14">
-        <v>1000</v>
-      </c>
-      <c r="C32" s="14">
-        <v>0.08</v>
-      </c>
-      <c r="D32" s="14">
-        <v>60000</v>
-      </c>
-      <c r="E32" s="14">
-        <v>120000</v>
-      </c>
-      <c r="F32" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G32" s="3">
-        <v>36.92</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2.52</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0.34</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0.39</v>
-      </c>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
       <c r="K32" s="9">
         <f>0.3*ABS(G32-36.3)/36.3 + 0.25*ABS(H32-2.56)/2.56 + 0.2*ABS(I32-0.25)/0.25 + 0.25*ABS(J32-0.34)/0.34</f>
-        <v>0.11779492282450174</v>
+        <v>1</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="M32" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="M32" s="17"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>23</v>
       </c>
-      <c r="B33" s="14">
-        <v>600</v>
-      </c>
-      <c r="C33" s="14">
-        <v>0.08</v>
-      </c>
-      <c r="D33" s="14">
-        <v>60000</v>
-      </c>
-      <c r="E33" s="14">
-        <v>120000</v>
-      </c>
-      <c r="F33" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G33" s="3">
-        <v>35.92</v>
-      </c>
-      <c r="H33" s="3">
-        <v>2.59</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0.31</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0.35</v>
-      </c>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
       <c r="K33" s="9">
         <f t="shared" ref="K33:K34" si="1">0.3*ABS(G33-36.3)/36.3 + 0.25*ABS(H33-2.56)/2.56 + 0.2*ABS(I33-0.25)/0.25 + 0.25*ABS(J33-0.34)/0.34</f>
-        <v>6.1423124544239094E-2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="M33" s="17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="M33" s="17"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>24</v>
       </c>
-      <c r="B34" s="14">
-        <v>800</v>
-      </c>
-      <c r="C34" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="D34" s="14">
-        <v>60000</v>
-      </c>
-      <c r="E34" s="14">
-        <v>120000</v>
-      </c>
-      <c r="F34" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G34" s="3">
-        <v>39.299999999999997</v>
-      </c>
-      <c r="H34" s="3">
-        <v>2.37</v>
-      </c>
-      <c r="I34" s="3">
-        <v>0.31</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0.39</v>
-      </c>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
       <c r="K34" s="9">
         <f t="shared" si="1"/>
-        <v>0.12811278181210498</v>
+        <v>1</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="M34" s="17" t="s">
-        <v>64</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M34" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Metrics/SFM_Calibration_narrow_door.xlsx
+++ b/Metrics/SFM_Calibration_narrow_door.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Piotr\CrowdEvacuation\Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404CDEE4-D025-42F0-8DFA-AB14C47A85F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4F2255-212D-462C-8ACF-CA7CC8ED384D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E00F018A-51B7-4FBE-B871-94FC33AFF981}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="73">
   <si>
     <t>#</t>
   </si>
@@ -47,9 +47,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>τ</t>
-  </si>
-  <si>
     <t>RSET [s]</t>
   </si>
   <si>
@@ -158,7 +155,106 @@
     <t>Fine tuning:</t>
   </si>
   <si>
-    <t>Stałe:  m=80kg, r=N(0.23,0.01) m, v₀=N(1.34,0.26) m/s</t>
+    <t>Stałe:  m=80kg, r=N(0.185,0.015) m, v₀=N(1.34,0.26) m/s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">τ                                                                                                                                                                       </t>
+  </si>
+  <si>
+    <t>kanoniczny z innym r - duze odstepy, lekkie drgania, odwracanie się agentow podczas ewakuacji, pod koniec jeszcze wieksze odstepy miedzy soba i spowolnienie</t>
+  </si>
+  <si>
+    <t>szybsze reakcje, szybsze wychodzenie, agenci nadal czasami się obraają, utrzymują duże odstępy, spowolnienie na koniec ale ne takie duże</t>
+  </si>
+  <si>
+    <t>większy ścisk, trochę agresywnie wychodzą, z tylu nadal duze odstepy</t>
+  </si>
+  <si>
+    <t>wiekszy scisk, dosyć naturalnie wychodzą, brka oscylacji lub artefaktow</t>
+  </si>
+  <si>
+    <t>jeszcze wiekszy scisk, czasem utrudnia wyjscie, odstepy wygladaja dosc naturalnie, nie ma aż tak duzego spowolnienia na koncu</t>
+  </si>
+  <si>
+    <t>na poczatku pojawily się oscylacje od za duzego scisku, symulacja wygląda dosyć dobrze</t>
+  </si>
+  <si>
+    <t>nienaturalny zbyt duzy scisk, blokowanie</t>
+  </si>
+  <si>
+    <t>szybsze poruszanie się w ścisku, większe odstępy</t>
+  </si>
+  <si>
+    <t>czasami odbijanie się od siebie, sprawna ewakuacja</t>
+  </si>
+  <si>
+    <t>mniejsze odstępy, podobnie jak wyżej</t>
+  </si>
+  <si>
+    <t>za duzy scisk przez co symulacja jest wolniejsza, blokuja się</t>
+  </si>
+  <si>
+    <t>jeszcze szybsze poruszanie się w ścisku, brak artefaktów</t>
+  </si>
+  <si>
+    <t>zdarzają się overlapy, szybka ewakuacja, większy ścisk</t>
+  </si>
+  <si>
+    <t>zbyt duży ścisk powodujący spowolnioną ewakuację</t>
+  </si>
+  <si>
+    <t>brak blokowania jak wyżej, szybkie reakcje, większe odstępy, spowolnienie pod koniec</t>
+  </si>
+  <si>
+    <t>sprawna ewakuacja, bez blokowania, racjonalne odstępy</t>
+  </si>
+  <si>
+    <t>znowu za duży ścisk spowalniający ewakuację</t>
+  </si>
+  <si>
+    <t>na początku zdarzyło się odpychanie do tyłu nienaturalne, zdecydowanie większe odstępy (nienaturalne)</t>
+  </si>
+  <si>
+    <t>odbijanie się od siebie, spowolnienie pod koniec</t>
+  </si>
+  <si>
+    <t>LC_001_SFM_cal_24</t>
+  </si>
+  <si>
+    <t>LC_001_SFM_cal_25</t>
+  </si>
+  <si>
+    <t>na początku kilka spowolnień, następnie płynna ewakuacja w ścisku</t>
+  </si>
+  <si>
+    <t>dobrze wyglądająca ewakuacja, sprawna, naturalnie wyglądające odstępy i ruchy</t>
+  </si>
+  <si>
+    <t>lekko się odbijają od siebie, naturalnie przechodzą</t>
+  </si>
+  <si>
+    <t>na początku blokowanie przez duży ścisk, potem odblokowanie i sprawne przejście</t>
+  </si>
+  <si>
+    <t>mocniejszy nacisk ale blokowanie się w pierwszej połowie symulacji</t>
+  </si>
+  <si>
+    <t>LC_001_SFM_cal_26</t>
+  </si>
+  <si>
+    <t>LC_001_SFM_cal_27</t>
+  </si>
+  <si>
+    <t>LC_001_SFM_cal_28</t>
+  </si>
+  <si>
+    <t>nienaturalne odbijanie się od siebie na początku</t>
+  </si>
+  <si>
+    <t>brak nienaturalnego odbijania się ale nadal duży nacisk który powoduje dłuższą ewakuację</t>
+  </si>
+  <si>
+    <t>na początku odpychanie do tyłu, w pewnym momencie nawet zablokowanie całkowite wymuszające ponowne uruchomienie, przepychanie tłumu na boki</t>
   </si>
 </sst>
 </file>
@@ -232,7 +328,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -261,6 +357,18 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -303,7 +411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -356,22 +464,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -709,7 +835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4E41E4-C8F6-4244-B955-9D9C71C2DB24}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
@@ -727,55 +853,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
+      <c r="A1" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
+      <c r="A2" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
+      <c r="A3" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -788,37 +914,37 @@
         <v>2</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -838,32 +964,34 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="5">
-        <v>69.5</v>
+        <v>105.54</v>
       </c>
       <c r="H6" s="5">
-        <v>1.34</v>
+        <v>0.88</v>
       </c>
       <c r="I6" s="5">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="J6" s="7">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="K6" s="6">
         <f>0.3*ABS(G6-36.3)/36.3 + 0.25*ABS(H6-2.56)/2.56 + 0.2*ABS(I6-0.25)/0.25 + 0.25*ABS(J6-0.34)/0.34</f>
-        <v>0.49710902558337383</v>
+        <v>0.90799978731161901</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="15"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2</v>
       </c>
       <c r="B7" s="14">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="C7" s="14">
         <v>0.08</v>
@@ -877,25 +1005,35 @@
       <c r="F7" s="14">
         <v>0.3</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
+      <c r="G7" s="8">
+        <v>77.930000000000007</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1.19</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0.24</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0.51</v>
+      </c>
       <c r="K7" s="9">
         <f t="shared" ref="K7:K26" si="0">0.3*ABS(G7-36.3)/36.3 + 0.25*ABS(H7-2.56)/2.56 + 0.2*ABS(I7-0.25)/0.25 + 0.25*ABS(J7-0.34)/0.34</f>
-        <v>1</v>
+        <v>0.6108386492768596</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="16"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>3</v>
       </c>
       <c r="B8" s="14">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="C8" s="14">
         <v>0.08</v>
@@ -907,30 +1045,40 @@
         <v>240000</v>
       </c>
       <c r="F8" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="8">
+        <v>64.53</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1.44</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0.24</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0.47</v>
+      </c>
       <c r="K8" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.44626902041808458</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="M8" s="16"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>4</v>
       </c>
       <c r="B9" s="14">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="C9" s="14">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="D9" s="14">
         <v>120000</v>
@@ -939,22 +1087,32 @@
         <v>240000</v>
       </c>
       <c r="F9" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="11">
+        <v>61.47</v>
+      </c>
+      <c r="H9" s="11">
+        <v>1.51</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="J9" s="11">
+        <v>0.45</v>
+      </c>
       <c r="K9" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.41543794436679632</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="M9" s="16"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>5</v>
       </c>
@@ -973,25 +1131,35 @@
       <c r="F10" s="14">
         <v>0.3</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
+      <c r="G10" s="8">
+        <v>56.97</v>
+      </c>
+      <c r="H10" s="8">
+        <v>1.63</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0.22</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0.42</v>
+      </c>
       <c r="K10" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.34447028819275644</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="16"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>6</v>
       </c>
       <c r="B11" s="14">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="C11" s="14">
         <v>0.08</v>
@@ -1003,30 +1171,40 @@
         <v>240000</v>
       </c>
       <c r="F11" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="8">
+        <v>56.27</v>
+      </c>
+      <c r="H11" s="8">
+        <v>1.65</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0.19</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0.4</v>
+      </c>
       <c r="K11" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.34602615687287319</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="16"/>
+        <v>14</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>7</v>
       </c>
       <c r="B12" s="14">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="C12" s="14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="D12" s="14">
         <v>120000</v>
@@ -1037,20 +1215,30 @@
       <c r="F12" s="14">
         <v>0.3</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="G12" s="8">
+        <v>63.08</v>
+      </c>
+      <c r="H12" s="8">
+        <v>1.47</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0.19</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0.38</v>
+      </c>
       <c r="K12" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.40517939125546915</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="M12" s="16"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>8</v>
       </c>
@@ -1061,525 +1249,935 @@
         <v>0.08</v>
       </c>
       <c r="D13" s="14">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="E13" s="14">
-        <v>240000</v>
+        <v>160000</v>
       </c>
       <c r="F13" s="14">
         <v>0.3</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
+      <c r="G13" s="8">
+        <v>61.52</v>
+      </c>
+      <c r="H13" s="8">
+        <v>1.51</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0.23</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0.46</v>
+      </c>
       <c r="K13" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.4152041086837629</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13" s="16"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>9</v>
       </c>
       <c r="B14" s="14">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="C14" s="14">
         <v>0.08</v>
       </c>
       <c r="D14" s="14">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="E14" s="14">
-        <v>240000</v>
+        <v>160000</v>
       </c>
       <c r="F14" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="8">
+        <v>53.6</v>
+      </c>
+      <c r="H14" s="8">
+        <v>1.74</v>
+      </c>
+      <c r="I14" s="8">
+        <v>0.23</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0.42</v>
+      </c>
       <c r="K14" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.29787686102333494</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M14" s="16"/>
+        <v>17</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>10</v>
       </c>
       <c r="B15" s="14">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="C15" s="14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="D15" s="14">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="E15" s="14">
-        <v>240000</v>
+        <v>160000</v>
       </c>
       <c r="F15" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="G15" s="11">
+        <v>55.77</v>
+      </c>
+      <c r="H15" s="11">
+        <v>1.67</v>
+      </c>
+      <c r="I15" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J15" s="11">
+        <v>0.4</v>
+      </c>
       <c r="K15" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.33194080046791452</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" s="16"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>11</v>
       </c>
       <c r="B16" s="14">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="C16" s="14">
         <v>0.08</v>
       </c>
       <c r="D16" s="14">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="E16" s="14">
-        <v>240000</v>
+        <v>160000</v>
       </c>
       <c r="F16" s="14">
         <v>0.3</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
+      <c r="G16" s="8">
+        <v>67.42</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1.38</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0.38</v>
+      </c>
       <c r="K16" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.48183622235051049</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="16"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>12</v>
       </c>
       <c r="B17" s="14">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="C17" s="14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="D17" s="14">
+        <v>60000</v>
+      </c>
+      <c r="E17" s="14">
         <v>120000</v>
       </c>
-      <c r="E17" s="14">
-        <v>240000</v>
-      </c>
       <c r="F17" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="G17" s="11">
+        <v>53.06</v>
+      </c>
+      <c r="H17" s="11">
+        <v>1.75</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="J17" s="11">
+        <v>0.45</v>
+      </c>
       <c r="K17" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.29849631213539141</v>
       </c>
       <c r="L17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="24">
+        <v>13</v>
+      </c>
+      <c r="B18" s="25">
+        <v>800</v>
+      </c>
+      <c r="C18" s="25">
+        <v>0.08</v>
+      </c>
+      <c r="D18" s="25">
+        <v>60000</v>
+      </c>
+      <c r="E18" s="25">
+        <v>120000</v>
+      </c>
+      <c r="F18" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="G18" s="26">
+        <v>50.93</v>
+      </c>
+      <c r="H18" s="26">
+        <v>1.83</v>
+      </c>
+      <c r="I18" s="26">
+        <v>0.24</v>
+      </c>
+      <c r="J18" s="26">
+        <v>0.43</v>
+      </c>
+      <c r="K18" s="27">
+        <f t="shared" si="0"/>
+        <v>0.2663746239973262</v>
+      </c>
+      <c r="L18" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="M17" s="16"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>13</v>
-      </c>
-      <c r="B18" s="14">
-        <v>1200</v>
-      </c>
-      <c r="C18" s="14">
-        <v>0.12</v>
-      </c>
-      <c r="D18" s="14">
-        <v>120000</v>
-      </c>
-      <c r="E18" s="14">
-        <v>240000</v>
-      </c>
-      <c r="F18" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" s="17"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M18" s="29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>14</v>
       </c>
       <c r="B19" s="14">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="C19" s="14">
         <v>0.08</v>
       </c>
       <c r="D19" s="14">
+        <v>60000</v>
+      </c>
+      <c r="E19" s="14">
         <v>120000</v>
       </c>
-      <c r="E19" s="14">
-        <v>240000</v>
-      </c>
       <c r="F19" s="14">
         <v>0.3</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="G19" s="3">
+        <v>56.27</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.4</v>
+      </c>
       <c r="K19" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.34602615687287319</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="17"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="M19" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>15</v>
       </c>
       <c r="B20" s="14">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="C20" s="14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="D20" s="14">
+        <v>60000</v>
+      </c>
+      <c r="E20" s="14">
         <v>120000</v>
       </c>
-      <c r="E20" s="14">
-        <v>240000</v>
-      </c>
       <c r="F20" s="14">
         <v>0.3</v>
       </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
+      <c r="G20" s="11">
+        <v>68.67</v>
+      </c>
+      <c r="H20" s="11">
+        <v>1.35</v>
+      </c>
+      <c r="I20" s="11">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J20" s="11">
+        <v>0.38</v>
+      </c>
       <c r="K20" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.50309648836290721</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M20" s="17"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="19">
+        <v>22</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="18">
         <v>16</v>
       </c>
-      <c r="B21" s="20">
-        <v>800</v>
-      </c>
-      <c r="C21" s="20">
+      <c r="B21" s="19">
+        <v>1200</v>
+      </c>
+      <c r="C21" s="19">
         <v>0.08</v>
       </c>
-      <c r="D21" s="20">
-        <v>60000</v>
-      </c>
-      <c r="E21" s="20">
-        <v>120000</v>
-      </c>
-      <c r="F21" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
+      <c r="D21" s="19">
+        <v>40000</v>
+      </c>
+      <c r="E21" s="19">
+        <v>80000</v>
+      </c>
+      <c r="F21" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="G21" s="20">
+        <v>62.75</v>
+      </c>
+      <c r="H21" s="20">
+        <v>1.48</v>
+      </c>
+      <c r="I21" s="20">
+        <v>0.24</v>
+      </c>
+      <c r="J21" s="20">
+        <v>0.45</v>
+      </c>
       <c r="K21" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L21" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="M21" s="23"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.41294614426349058</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>17</v>
       </c>
       <c r="B22" s="14">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="C22" s="14">
         <v>0.08</v>
       </c>
       <c r="D22" s="14">
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="E22" s="14">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="F22" s="14">
         <v>0.3</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
+      <c r="G22" s="3">
+        <v>50.89</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1.83</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.42</v>
+      </c>
       <c r="K22" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.27469110430845894</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M22" s="17"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="M22" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>18</v>
       </c>
       <c r="B23" s="14">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="C23" s="14">
         <v>0.08</v>
       </c>
       <c r="D23" s="14">
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="E23" s="14">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="F23" s="14">
         <v>0.3</v>
       </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
+      <c r="G23" s="3">
+        <v>55.15</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1.69</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.41</v>
+      </c>
       <c r="K23" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.34021664970223625</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M23" s="17"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="M23" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>19</v>
       </c>
       <c r="B24" s="14">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="C24" s="14">
         <v>0.08</v>
       </c>
       <c r="D24" s="14">
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="E24" s="14">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="F24" s="14">
         <v>0.3</v>
       </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
+      <c r="G24" s="3">
+        <v>60.63</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1.53</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.38</v>
+      </c>
       <c r="K24" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.4030720823711717</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="M24" s="17"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="M24" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>20</v>
       </c>
       <c r="B25" s="14">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="C25" s="14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="D25" s="14">
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="E25" s="14">
-        <v>120000</v>
+        <v>240000</v>
       </c>
       <c r="F25" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="G25" s="3">
+        <v>63.96</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1.45</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.45</v>
+      </c>
       <c r="K25" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.44187583176349055</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M25" s="17"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="M25" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>21</v>
       </c>
       <c r="B26" s="14">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="C26" s="14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="D26" s="14">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="E26" s="14">
-        <v>120000</v>
+        <v>160000</v>
       </c>
       <c r="F26" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="3">
+        <v>65.739999999999995</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1.41</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0.44</v>
+      </c>
       <c r="K26" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.45313988438867281</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M26" s="17"/>
+        <v>34</v>
+      </c>
+      <c r="M26" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="23"/>
+    </row>
+    <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>22</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
+      <c r="B32" s="14">
+        <v>800</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0.06</v>
+      </c>
+      <c r="D32" s="14">
+        <v>60000</v>
+      </c>
+      <c r="E32" s="14">
+        <v>120000</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="G32" s="3">
+        <v>51.03</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1.82</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0.4</v>
+      </c>
       <c r="K32" s="9">
         <f>0.3*ABS(G32-36.3)/36.3 + 0.25*ABS(H32-2.56)/2.56 + 0.2*ABS(I32-0.25)/0.25 + 0.25*ABS(J32-0.34)/0.34</f>
-        <v>1</v>
+        <v>0.26211880924890618</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M32" s="17"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="M32" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>23</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
+      <c r="B33" s="14">
+        <v>800</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0.06</v>
+      </c>
+      <c r="D33" s="14">
+        <v>40000</v>
+      </c>
+      <c r="E33" s="14">
+        <v>80000</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="G33" s="3">
+        <v>48.84</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.41</v>
+      </c>
       <c r="K33" s="9">
-        <f t="shared" ref="K33:K34" si="1">0.3*ABS(G33-36.3)/36.3 + 0.25*ABS(H33-2.56)/2.56 + 0.2*ABS(I33-0.25)/0.25 + 0.25*ABS(J33-0.34)/0.34</f>
-        <v>1</v>
+        <f t="shared" ref="K33:K36" si="1">0.3*ABS(G33-36.3)/36.3 + 0.25*ABS(H33-2.56)/2.56 + 0.2*ABS(I33-0.25)/0.25 + 0.25*ABS(J33-0.34)/0.34</f>
+        <v>0.23556007687165775</v>
       </c>
       <c r="L33" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M33" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="24">
+        <v>24</v>
+      </c>
+      <c r="B34" s="25">
+        <v>800</v>
+      </c>
+      <c r="C34" s="25">
+        <v>0.04</v>
+      </c>
+      <c r="D34" s="25">
+        <v>60000</v>
+      </c>
+      <c r="E34" s="25">
+        <v>120000</v>
+      </c>
+      <c r="F34" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="G34" s="26">
+        <v>48.76</v>
+      </c>
+      <c r="H34" s="26">
+        <v>1.91</v>
+      </c>
+      <c r="I34" s="26">
+        <v>0.23</v>
+      </c>
+      <c r="J34" s="26">
+        <v>0.4</v>
+      </c>
+      <c r="K34" s="27">
+        <f t="shared" si="1"/>
+        <v>0.22656941617039378</v>
+      </c>
+      <c r="L34" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="M33" s="17"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>24</v>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="9">
+      <c r="M34" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>25</v>
+      </c>
+      <c r="B35" s="14">
+        <v>800</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="D35" s="14">
+        <v>40000</v>
+      </c>
+      <c r="E35" s="14">
+        <v>80000</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="G35" s="3">
+        <v>54</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1.72</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="K35" s="9">
+        <f>0.3*ABS(G35-36.3)/36.3 + 0.25*ABS(H35-2.56)/2.56 + 0.2*ABS(I35-0.25)/0.25 + 0.25*ABS(J35-0.34)/0.34</f>
+        <v>0.30507694761789012</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M35" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>26</v>
+      </c>
+      <c r="B36" s="14">
+        <v>800</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0.06</v>
+      </c>
+      <c r="D36" s="14">
+        <v>50000</v>
+      </c>
+      <c r="E36" s="14">
+        <v>100000</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="G36" s="3">
+        <v>53.66</v>
+      </c>
+      <c r="H36" s="3">
+        <v>1.73</v>
+      </c>
+      <c r="I36" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="K36" s="9">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L34" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M34" s="17"/>
+        <v>0.31664340893898885</v>
+      </c>
+      <c r="L36" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>27</v>
+      </c>
+      <c r="B37" s="14">
+        <v>800</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="D37" s="14">
+        <v>60000</v>
+      </c>
+      <c r="E37" s="14">
+        <v>120000</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="G37" s="3">
+        <v>48.92</v>
+      </c>
+      <c r="H37" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="I37" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="K37" s="9">
+        <f t="shared" ref="K37:K39" si="2">0.3*ABS(G37-36.3)/36.3 + 0.25*ABS(H37-2.56)/2.56 + 0.2*ABS(I37-0.25)/0.25 + 0.25*ABS(J37-0.34)/0.34</f>
+        <v>0.20616241036703942</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M37" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>28</v>
+      </c>
+      <c r="B38" s="14">
+        <v>1000</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="D38" s="14">
+        <v>60000</v>
+      </c>
+      <c r="E38" s="14">
+        <v>120000</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="G38" s="3">
+        <v>49.28</v>
+      </c>
+      <c r="H38" s="3">
+        <v>1.89</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="K38" s="9">
+        <f t="shared" si="2"/>
+        <v>0.24017300300802139</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M38" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>29</v>
+      </c>
+      <c r="B39" s="14">
+        <v>1000</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="D39" s="14">
+        <v>60000</v>
+      </c>
+      <c r="E39" s="14">
+        <v>120000</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="G39" s="3">
+        <v>42.98</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="J39" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="K39" s="9">
+        <f t="shared" si="2"/>
+        <v>0.17968087627613025</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M39" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Metrics/SFM_Calibration_narrow_door.xlsx
+++ b/Metrics/SFM_Calibration_narrow_door.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Piotr\CrowdEvacuation\Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4F2255-212D-462C-8ACF-CA7CC8ED384D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465E991D-180D-407E-9CFD-2C3F7CD2F707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E00F018A-51B7-4FBE-B871-94FC33AFF981}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{E00F018A-51B7-4FBE-B871-94FC33AFF981}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -122,9 +122,6 @@
     <t>Mean headway [m]</t>
   </si>
   <si>
-    <t>Cel empiryczny (Ghost LC_001): RSET=36.3s, throughput=2.56 ped/s, mean_speed=0.25 m/s, mean_headway=0,34 m</t>
-  </si>
-  <si>
     <t>k</t>
   </si>
   <si>
@@ -255,6 +252,9 @@
   </si>
   <si>
     <t>na początku odpychanie do tyłu, w pewnym momencie nawet zablokowanie całkowite wymuszające ponowne uruchomienie, przepychanie tłumu na boki</t>
+  </si>
+  <si>
+    <t>Cel empiryczny (Ghost LC_001): RSET=36.3s, throughput=2.56 ped/s, mean_speed=0.37 m/s, mean_headway=0,31 m</t>
   </si>
 </sst>
 </file>
@@ -328,7 +328,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,12 +363,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -411,7 +405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -479,26 +473,23 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -853,55 +844,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
+      <c r="A2" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
+      <c r="A3" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -914,13 +905,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>30</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>3</v>
@@ -963,27 +954,19 @@
       <c r="F6" s="13">
         <v>0.5</v>
       </c>
-      <c r="G6" s="5">
-        <v>105.54</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0.88</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0.21</v>
-      </c>
-      <c r="J6" s="7">
-        <v>0.53</v>
-      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="7"/>
       <c r="K6" s="6">
-        <f>0.3*ABS(G6-36.3)/36.3 + 0.25*ABS(H6-2.56)/2.56 + 0.2*ABS(I6-0.25)/0.25 + 0.25*ABS(J6-0.34)/0.34</f>
-        <v>0.90799978731161901</v>
+        <f>0.3*ABS(G6-36.3)/36.3 + 0.25*ABS(H6-2.56)/2.56 + 0.2*ABS(I6-0.37)/0.37 + 0.25*ABS(J6-0.31)/0.31</f>
+        <v>1</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -1005,27 +988,19 @@
       <c r="F7" s="14">
         <v>0.3</v>
       </c>
-      <c r="G7" s="8">
-        <v>77.930000000000007</v>
-      </c>
-      <c r="H7" s="8">
-        <v>1.19</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0.24</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0.51</v>
-      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
       <c r="K7" s="9">
-        <f t="shared" ref="K7:K26" si="0">0.3*ABS(G7-36.3)/36.3 + 0.25*ABS(H7-2.56)/2.56 + 0.2*ABS(I7-0.25)/0.25 + 0.25*ABS(J7-0.34)/0.34</f>
-        <v>0.6108386492768596</v>
+        <f t="shared" ref="K7:K26" si="0">0.3*ABS(G7-36.3)/36.3 + 0.25*ABS(H7-2.56)/2.56 + 0.2*ABS(I7-0.37)/0.37 + 0.25*ABS(J7-0.31)/0.31</f>
+        <v>1</v>
       </c>
       <c r="L7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1047,27 +1022,19 @@
       <c r="F8" s="14">
         <v>0.3</v>
       </c>
-      <c r="G8" s="8">
-        <v>64.53</v>
-      </c>
-      <c r="H8" s="8">
-        <v>1.44</v>
-      </c>
-      <c r="I8" s="8">
-        <v>0.24</v>
-      </c>
-      <c r="J8" s="8">
-        <v>0.47</v>
-      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
       <c r="K8" s="9">
         <f t="shared" si="0"/>
-        <v>0.44626902041808458</v>
+        <v>1</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>11</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1089,27 +1056,19 @@
       <c r="F9" s="14">
         <v>0.3</v>
       </c>
-      <c r="G9" s="11">
-        <v>61.47</v>
-      </c>
-      <c r="H9" s="11">
-        <v>1.51</v>
-      </c>
-      <c r="I9" s="11">
-        <v>0.22</v>
-      </c>
-      <c r="J9" s="11">
-        <v>0.45</v>
-      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
       <c r="K9" s="9">
         <f t="shared" si="0"/>
-        <v>0.41543794436679632</v>
+        <v>1</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -1131,27 +1090,19 @@
       <c r="F10" s="14">
         <v>0.3</v>
       </c>
-      <c r="G10" s="8">
-        <v>56.97</v>
-      </c>
-      <c r="H10" s="8">
-        <v>1.63</v>
-      </c>
-      <c r="I10" s="8">
-        <v>0.22</v>
-      </c>
-      <c r="J10" s="8">
-        <v>0.42</v>
-      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
       <c r="K10" s="9">
         <f t="shared" si="0"/>
-        <v>0.34447028819275644</v>
+        <v>1</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1173,27 +1124,19 @@
       <c r="F11" s="14">
         <v>0.3</v>
       </c>
-      <c r="G11" s="8">
-        <v>56.27</v>
-      </c>
-      <c r="H11" s="8">
-        <v>1.65</v>
-      </c>
-      <c r="I11" s="8">
-        <v>0.19</v>
-      </c>
-      <c r="J11" s="8">
-        <v>0.4</v>
-      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
       <c r="K11" s="9">
         <f t="shared" si="0"/>
-        <v>0.34602615687287319</v>
+        <v>1</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1215,27 +1158,19 @@
       <c r="F12" s="14">
         <v>0.3</v>
       </c>
-      <c r="G12" s="8">
-        <v>63.08</v>
-      </c>
-      <c r="H12" s="8">
-        <v>1.47</v>
-      </c>
-      <c r="I12" s="8">
-        <v>0.19</v>
-      </c>
-      <c r="J12" s="8">
-        <v>0.38</v>
-      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
       <c r="K12" s="9">
         <f t="shared" si="0"/>
-        <v>0.40517939125546915</v>
+        <v>1</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>15</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1257,27 +1192,19 @@
       <c r="F13" s="14">
         <v>0.3</v>
       </c>
-      <c r="G13" s="8">
-        <v>61.52</v>
-      </c>
-      <c r="H13" s="8">
-        <v>1.51</v>
-      </c>
-      <c r="I13" s="8">
-        <v>0.23</v>
-      </c>
-      <c r="J13" s="8">
-        <v>0.46</v>
-      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
       <c r="K13" s="9">
         <f t="shared" si="0"/>
-        <v>0.4152041086837629</v>
+        <v>1</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>16</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1299,27 +1226,19 @@
       <c r="F14" s="14">
         <v>0.3</v>
       </c>
-      <c r="G14" s="8">
-        <v>53.6</v>
-      </c>
-      <c r="H14" s="8">
-        <v>1.74</v>
-      </c>
-      <c r="I14" s="8">
-        <v>0.23</v>
-      </c>
-      <c r="J14" s="8">
-        <v>0.42</v>
-      </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
       <c r="K14" s="9">
         <f t="shared" si="0"/>
-        <v>0.29787686102333494</v>
+        <v>1</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>17</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1341,27 +1260,19 @@
       <c r="F15" s="14">
         <v>0.3</v>
       </c>
-      <c r="G15" s="11">
-        <v>55.77</v>
-      </c>
-      <c r="H15" s="11">
-        <v>1.67</v>
-      </c>
-      <c r="I15" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="J15" s="11">
-        <v>0.4</v>
-      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
       <c r="K15" s="9">
         <f t="shared" si="0"/>
-        <v>0.33194080046791452</v>
+        <v>1</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>18</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1383,27 +1294,19 @@
       <c r="F16" s="14">
         <v>0.3</v>
       </c>
-      <c r="G16" s="8">
-        <v>67.42</v>
-      </c>
-      <c r="H16" s="8">
-        <v>1.38</v>
-      </c>
-      <c r="I16" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="J16" s="8">
-        <v>0.38</v>
-      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
       <c r="K16" s="9">
         <f t="shared" si="0"/>
-        <v>0.48183622235051049</v>
+        <v>1</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1425,69 +1328,53 @@
       <c r="F17" s="14">
         <v>0.3</v>
       </c>
-      <c r="G17" s="11">
-        <v>53.06</v>
-      </c>
-      <c r="H17" s="11">
-        <v>1.75</v>
-      </c>
-      <c r="I17" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="J17" s="11">
-        <v>0.45</v>
-      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
       <c r="K17" s="9">
         <f t="shared" si="0"/>
-        <v>0.29849631213539141</v>
+        <v>1</v>
       </c>
       <c r="L17" s="10" t="s">
         <v>20</v>
       </c>
       <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="23">
+        <v>13</v>
+      </c>
+      <c r="B18" s="24">
+        <v>800</v>
+      </c>
+      <c r="C18" s="24">
+        <v>0.08</v>
+      </c>
+      <c r="D18" s="24">
+        <v>60000</v>
+      </c>
+      <c r="E18" s="24">
+        <v>120000</v>
+      </c>
+      <c r="F18" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L18" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="27" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="24">
-        <v>13</v>
-      </c>
-      <c r="B18" s="25">
-        <v>800</v>
-      </c>
-      <c r="C18" s="25">
-        <v>0.08</v>
-      </c>
-      <c r="D18" s="25">
-        <v>60000</v>
-      </c>
-      <c r="E18" s="25">
-        <v>120000</v>
-      </c>
-      <c r="F18" s="25">
-        <v>0.3</v>
-      </c>
-      <c r="G18" s="26">
-        <v>50.93</v>
-      </c>
-      <c r="H18" s="26">
-        <v>1.83</v>
-      </c>
-      <c r="I18" s="26">
-        <v>0.24</v>
-      </c>
-      <c r="J18" s="26">
-        <v>0.43</v>
-      </c>
-      <c r="K18" s="27">
-        <f t="shared" si="0"/>
-        <v>0.2663746239973262</v>
-      </c>
-      <c r="L18" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="29" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1509,27 +1396,19 @@
       <c r="F19" s="14">
         <v>0.3</v>
       </c>
-      <c r="G19" s="3">
-        <v>56.27</v>
-      </c>
-      <c r="H19" s="3">
-        <v>1.65</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0.19</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0.4</v>
-      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
       <c r="K19" s="9">
         <f t="shared" si="0"/>
-        <v>0.34602615687287319</v>
+        <v>1</v>
       </c>
       <c r="L19" s="10" t="s">
         <v>25</v>
       </c>
       <c r="M19" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1551,27 +1430,19 @@
       <c r="F20" s="14">
         <v>0.3</v>
       </c>
-      <c r="G20" s="11">
-        <v>68.67</v>
-      </c>
-      <c r="H20" s="11">
-        <v>1.35</v>
-      </c>
-      <c r="I20" s="11">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="J20" s="11">
-        <v>0.38</v>
-      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
       <c r="K20" s="9">
         <f t="shared" si="0"/>
-        <v>0.50309648836290721</v>
+        <v>1</v>
       </c>
       <c r="L20" s="10" t="s">
         <v>22</v>
       </c>
       <c r="M20" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1593,27 +1464,19 @@
       <c r="F21" s="19">
         <v>0.3</v>
       </c>
-      <c r="G21" s="20">
-        <v>62.75</v>
-      </c>
-      <c r="H21" s="20">
-        <v>1.48</v>
-      </c>
-      <c r="I21" s="20">
-        <v>0.24</v>
-      </c>
-      <c r="J21" s="20">
-        <v>0.45</v>
-      </c>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
       <c r="K21" s="9">
         <f t="shared" si="0"/>
-        <v>0.41294614426349058</v>
+        <v>1</v>
       </c>
       <c r="L21" s="21" t="s">
         <v>23</v>
       </c>
       <c r="M21" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1635,27 +1498,19 @@
       <c r="F22" s="14">
         <v>0.3</v>
       </c>
-      <c r="G22" s="3">
-        <v>50.89</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1.83</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0.22</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0.42</v>
-      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
       <c r="K22" s="9">
         <f t="shared" si="0"/>
-        <v>0.27469110430845894</v>
+        <v>1</v>
       </c>
       <c r="L22" s="10" t="s">
         <v>24</v>
       </c>
       <c r="M22" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1677,27 +1532,19 @@
       <c r="F23" s="14">
         <v>0.3</v>
       </c>
-      <c r="G23" s="3">
-        <v>55.15</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1.69</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0.19</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0.41</v>
-      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
       <c r="K23" s="9">
         <f t="shared" si="0"/>
-        <v>0.34021664970223625</v>
+        <v>1</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1719,27 +1566,19 @@
       <c r="F24" s="14">
         <v>0.3</v>
       </c>
-      <c r="G24" s="3">
-        <v>60.63</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1.53</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0.38</v>
-      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
       <c r="K24" s="9">
         <f t="shared" si="0"/>
-        <v>0.4030720823711717</v>
+        <v>1</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1761,27 +1600,19 @@
       <c r="F25" s="14">
         <v>0.5</v>
       </c>
-      <c r="G25" s="3">
-        <v>63.96</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1.45</v>
-      </c>
-      <c r="I25" s="3">
-        <v>0.22</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0.45</v>
-      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
       <c r="K25" s="9">
         <f t="shared" si="0"/>
-        <v>0.44187583176349055</v>
+        <v>1</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1803,45 +1634,37 @@
       <c r="F26" s="14">
         <v>0.5</v>
       </c>
-      <c r="G26" s="3">
-        <v>65.739999999999995</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1.41</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0.22</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0.44</v>
-      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
       <c r="K26" s="9">
         <f t="shared" si="0"/>
-        <v>0.45313988438867281</v>
+        <v>1</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M26" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
+      <c r="A30" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="28"/>
     </row>
     <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
@@ -1862,27 +1685,19 @@
       <c r="F32" s="14">
         <v>0.3</v>
       </c>
-      <c r="G32" s="3">
-        <v>51.03</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1.82</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0.22</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0.4</v>
-      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
       <c r="K32" s="9">
-        <f>0.3*ABS(G32-36.3)/36.3 + 0.25*ABS(H32-2.56)/2.56 + 0.2*ABS(I32-0.25)/0.25 + 0.25*ABS(J32-0.34)/0.34</f>
-        <v>0.26211880924890618</v>
+        <f>0.3*ABS(G32-36.3)/36.3 + 0.25*ABS(H32-2.56)/2.56 + 0.2*ABS(I32-0.37)/0.37 + 0.25*ABS(J32-0.31)/0.31</f>
+        <v>1</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M32" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1904,69 +1719,53 @@
       <c r="F33" s="14">
         <v>0.3</v>
       </c>
-      <c r="G33" s="3">
-        <v>48.84</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0.41</v>
-      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
       <c r="K33" s="9">
-        <f t="shared" ref="K33:K36" si="1">0.3*ABS(G33-36.3)/36.3 + 0.25*ABS(H33-2.56)/2.56 + 0.2*ABS(I33-0.25)/0.25 + 0.25*ABS(J33-0.34)/0.34</f>
-        <v>0.23556007687165775</v>
+        <f t="shared" ref="K33:K39" si="1">0.3*ABS(G33-36.3)/36.3 + 0.25*ABS(H33-2.56)/2.56 + 0.2*ABS(I33-0.37)/0.37 + 0.25*ABS(J33-0.31)/0.31</f>
+        <v>1</v>
       </c>
       <c r="L33" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="M33" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="23">
+        <v>24</v>
+      </c>
+      <c r="B34" s="24">
+        <v>800</v>
+      </c>
+      <c r="C34" s="24">
+        <v>0.04</v>
+      </c>
+      <c r="D34" s="24">
+        <v>60000</v>
+      </c>
+      <c r="E34" s="24">
+        <v>120000</v>
+      </c>
+      <c r="F34" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L34" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M33" s="17" t="s">
+      <c r="M34" s="27" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="24">
-        <v>24</v>
-      </c>
-      <c r="B34" s="25">
-        <v>800</v>
-      </c>
-      <c r="C34" s="25">
-        <v>0.04</v>
-      </c>
-      <c r="D34" s="25">
-        <v>60000</v>
-      </c>
-      <c r="E34" s="25">
-        <v>120000</v>
-      </c>
-      <c r="F34" s="25">
-        <v>0.3</v>
-      </c>
-      <c r="G34" s="26">
-        <v>48.76</v>
-      </c>
-      <c r="H34" s="26">
-        <v>1.91</v>
-      </c>
-      <c r="I34" s="26">
-        <v>0.23</v>
-      </c>
-      <c r="J34" s="26">
-        <v>0.4</v>
-      </c>
-      <c r="K34" s="27">
-        <f t="shared" si="1"/>
-        <v>0.22656941617039378</v>
-      </c>
-      <c r="L34" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="M34" s="29" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1988,27 +1787,19 @@
       <c r="F35" s="14">
         <v>0.3</v>
       </c>
-      <c r="G35" s="3">
-        <v>54</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1.72</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0.39</v>
-      </c>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
       <c r="K35" s="9">
-        <f>0.3*ABS(G35-36.3)/36.3 + 0.25*ABS(H35-2.56)/2.56 + 0.2*ABS(I35-0.25)/0.25 + 0.25*ABS(J35-0.34)/0.34</f>
-        <v>0.30507694761789012</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M35" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -2030,27 +1821,19 @@
       <c r="F36" s="14">
         <v>0.25</v>
       </c>
-      <c r="G36" s="3">
-        <v>53.66</v>
-      </c>
-      <c r="H36" s="3">
-        <v>1.73</v>
-      </c>
-      <c r="I36" s="3">
-        <v>0.19</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0.4</v>
-      </c>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
       <c r="K36" s="9">
         <f t="shared" si="1"/>
-        <v>0.31664340893898885</v>
+        <v>1</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M36" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -2072,27 +1855,19 @@
       <c r="F37" s="14">
         <v>0.3</v>
       </c>
-      <c r="G37" s="3">
-        <v>48.92</v>
-      </c>
-      <c r="H37" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="I37" s="3">
-        <v>0.24</v>
-      </c>
-      <c r="J37" s="3">
-        <v>0.38</v>
-      </c>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
       <c r="K37" s="9">
-        <f t="shared" ref="K37:K39" si="2">0.3*ABS(G37-36.3)/36.3 + 0.25*ABS(H37-2.56)/2.56 + 0.2*ABS(I37-0.25)/0.25 + 0.25*ABS(J37-0.34)/0.34</f>
-        <v>0.20616241036703942</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M37" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -2114,27 +1889,19 @@
       <c r="F38" s="14">
         <v>0.3</v>
       </c>
-      <c r="G38" s="3">
-        <v>49.28</v>
-      </c>
-      <c r="H38" s="3">
-        <v>1.89</v>
-      </c>
-      <c r="I38" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="J38" s="3">
-        <v>0.41</v>
-      </c>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
       <c r="K38" s="9">
-        <f t="shared" si="2"/>
-        <v>0.24017300300802139</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M38" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="72" x14ac:dyDescent="0.3">
@@ -2156,27 +1923,19 @@
       <c r="F39" s="14">
         <v>0.3</v>
       </c>
-      <c r="G39" s="3">
-        <v>42.98</v>
-      </c>
-      <c r="H39" s="3">
-        <v>2.16</v>
-      </c>
-      <c r="I39" s="3">
-        <v>0.32</v>
-      </c>
-      <c r="J39" s="3">
-        <v>0.38</v>
-      </c>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
       <c r="K39" s="9">
-        <f t="shared" si="2"/>
-        <v>0.17968087627613025</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M39" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Metrics/SFM_Calibration_narrow_door.xlsx
+++ b/Metrics/SFM_Calibration_narrow_door.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Piotr\CrowdEvacuation\Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465E991D-180D-407E-9CFD-2C3F7CD2F707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDB8639-7E60-4C08-95A9-13DF55BD10DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{E00F018A-51B7-4FBE-B871-94FC33AFF981}"/>
+    <workbookView xWindow="-28920" yWindow="-165" windowWidth="29040" windowHeight="15720" xr2:uid="{E00F018A-51B7-4FBE-B871-94FC33AFF981}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
   <si>
     <t>#</t>
   </si>
@@ -155,106 +155,88 @@
     <t>Stałe:  m=80kg, r=N(0.185,0.015) m, v₀=N(1.34,0.26) m/s</t>
   </si>
   <si>
-    <t xml:space="preserve">τ                                                                                                                                                                       </t>
-  </si>
-  <si>
-    <t>kanoniczny z innym r - duze odstepy, lekkie drgania, odwracanie się agentow podczas ewakuacji, pod koniec jeszcze wieksze odstepy miedzy soba i spowolnienie</t>
-  </si>
-  <si>
     <t>szybsze reakcje, szybsze wychodzenie, agenci nadal czasami się obraają, utrzymują duże odstępy, spowolnienie na koniec ale ne takie duże</t>
   </si>
   <si>
     <t>większy ścisk, trochę agresywnie wychodzą, z tylu nadal duze odstepy</t>
   </si>
   <si>
-    <t>wiekszy scisk, dosyć naturalnie wychodzą, brka oscylacji lub artefaktow</t>
-  </si>
-  <si>
-    <t>jeszcze wiekszy scisk, czasem utrudnia wyjscie, odstepy wygladaja dosc naturalnie, nie ma aż tak duzego spowolnienia na koncu</t>
-  </si>
-  <si>
-    <t>na poczatku pojawily się oscylacje od za duzego scisku, symulacja wygląda dosyć dobrze</t>
-  </si>
-  <si>
-    <t>nienaturalny zbyt duzy scisk, blokowanie</t>
-  </si>
-  <si>
-    <t>szybsze poruszanie się w ścisku, większe odstępy</t>
-  </si>
-  <si>
-    <t>czasami odbijanie się od siebie, sprawna ewakuacja</t>
-  </si>
-  <si>
-    <t>mniejsze odstępy, podobnie jak wyżej</t>
-  </si>
-  <si>
-    <t>za duzy scisk przez co symulacja jest wolniejsza, blokuja się</t>
-  </si>
-  <si>
-    <t>jeszcze szybsze poruszanie się w ścisku, brak artefaktów</t>
-  </si>
-  <si>
-    <t>zdarzają się overlapy, szybka ewakuacja, większy ścisk</t>
-  </si>
-  <si>
-    <t>zbyt duży ścisk powodujący spowolnioną ewakuację</t>
-  </si>
-  <si>
-    <t>brak blokowania jak wyżej, szybkie reakcje, większe odstępy, spowolnienie pod koniec</t>
-  </si>
-  <si>
-    <t>sprawna ewakuacja, bez blokowania, racjonalne odstępy</t>
-  </si>
-  <si>
-    <t>znowu za duży ścisk spowalniający ewakuację</t>
-  </si>
-  <si>
-    <t>na początku zdarzyło się odpychanie do tyłu nienaturalne, zdecydowanie większe odstępy (nienaturalne)</t>
-  </si>
-  <si>
-    <t>odbijanie się od siebie, spowolnienie pod koniec</t>
-  </si>
-  <si>
     <t>LC_001_SFM_cal_24</t>
   </si>
   <si>
-    <t>LC_001_SFM_cal_25</t>
-  </si>
-  <si>
-    <t>na początku kilka spowolnień, następnie płynna ewakuacja w ścisku</t>
-  </si>
-  <si>
-    <t>dobrze wyglądająca ewakuacja, sprawna, naturalnie wyglądające odstępy i ruchy</t>
-  </si>
-  <si>
-    <t>lekko się odbijają od siebie, naturalnie przechodzą</t>
-  </si>
-  <si>
-    <t>na początku blokowanie przez duży ścisk, potem odblokowanie i sprawne przejście</t>
-  </si>
-  <si>
-    <t>mocniejszy nacisk ale blokowanie się w pierwszej połowie symulacji</t>
-  </si>
-  <si>
-    <t>LC_001_SFM_cal_26</t>
-  </si>
-  <si>
-    <t>LC_001_SFM_cal_27</t>
-  </si>
-  <si>
-    <t>LC_001_SFM_cal_28</t>
-  </si>
-  <si>
-    <t>nienaturalne odbijanie się od siebie na początku</t>
-  </si>
-  <si>
-    <t>brak nienaturalnego odbijania się ale nadal duży nacisk który powoduje dłuższą ewakuację</t>
-  </si>
-  <si>
-    <t>na początku odpychanie do tyłu, w pewnym momencie nawet zablokowanie całkowite wymuszające ponowne uruchomienie, przepychanie tłumu na boki</t>
-  </si>
-  <si>
     <t>Cel empiryczny (Ghost LC_001): RSET=36.3s, throughput=2.56 ped/s, mean_speed=0.37 m/s, mean_headway=0,31 m</t>
+  </si>
+  <si>
+    <t>τ</t>
+  </si>
+  <si>
+    <t>kanoniczny z innym r - duze odstepy, lekkie drgania, odwracanie się agentow podczas ewakuacji, pod koniec jeszcze wieksze odstepy miedzy soba i spowolnienie, duże problemy z ukończeniem symulacji</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>wiekszy scisk, pojawiły się oscylacje i artefakty w postaci odpychania do tyłu, lekkie wystrzeliwywanie - ale tylko do połowy symulacji</t>
+  </si>
+  <si>
+    <t>jeszcze wiekszy scisk, większe artefakty, drżenie, odpychanie do tyłu</t>
+  </si>
+  <si>
+    <t>to samo co wyżej lecz jeszcze gorzej i mniej realnie</t>
+  </si>
+  <si>
+    <t>niewiele powyższych artefaktów, szybsze poruszanie się w ścisku, większe odstępy, lekkie ślizganie się, zwolnienie pod koniec</t>
+  </si>
+  <si>
+    <t>odbijanie się od siebie - artefakty, sprawna ewakuacja</t>
+  </si>
+  <si>
+    <t>większe odstępy i brak artefaktów, sprawna ewakuacja, czasami agresywne zderzenia</t>
+  </si>
+  <si>
+    <t>mniejsze A = oscylacje i artefakty w postaci drżenia i odpychania jak w eksperymentach powyżej</t>
+  </si>
+  <si>
+    <t>szybkie poruszanie się w ścisku, pojedyncze, rzadkie artefakty lecz spowolnienie pod koniec</t>
+  </si>
+  <si>
+    <t>duże odstępy spowodowane dużym B, brak artefaktów, nierealne rozstawienie, jeszcze większe odstępy pod koniec uniemożliwiające ukończenie symulacji</t>
+  </si>
+  <si>
+    <t>zbyt duży ścisk i artefakty z powodu małego A jak wyżej</t>
+  </si>
+  <si>
+    <t>odrzucanie tłumu do tyłu i na boki (lekko), szybka ewakuacja i niewielkie spowolnienie na końcu</t>
+  </si>
+  <si>
+    <t>brak artefaktów i odpychania, realne odstępy (mogłyby być mniejsze), spowolnienie pod koniec</t>
+  </si>
+  <si>
+    <t>nierealna symulacja przez artefakty, bardzo duże odrzucanie</t>
+  </si>
+  <si>
+    <t>duży ścisk i brak artefaktów, lekkie blokowanie ale ogólnie pozytywne wrażenie, brak spowolnienia na końcu</t>
+  </si>
+  <si>
+    <t>ogromne, nierealne odstępy</t>
+  </si>
+  <si>
+    <t>oscylacje, odrzucanie, artefakty, odstępy, spowolnienie pod koniec</t>
+  </si>
+  <si>
+    <t>artefakty głównie na samym początku, następnie sprawna ewakuacja lecz dosyć duże odstępy</t>
+  </si>
+  <si>
+    <t>szybka sprawna ewakuacja, kilka razy tłum został odepchnięty w tył/bok, racjonalne odstępy, spwoolnienie pod koniec</t>
+  </si>
+  <si>
+    <t>więcej odpychania na boki, zbyt dużo przez co symulacja nie wygląda realnie</t>
+  </si>
+  <si>
+    <t>na początku lekkie odpychanie, duży ścisk, w późniejszej fazie kilka kolejnych artefaktów</t>
+  </si>
+  <si>
+    <t>duży ścisk i sprawność, brak artefaktów, bardzo dobre wizualnie</t>
   </si>
 </sst>
 </file>
@@ -264,7 +246,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,8 +309,15 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,8 +350,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -405,7 +400,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -419,9 +414,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -473,6 +465,33 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -480,6 +499,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,74 +849,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4E41E4-C8F6-4244-B955-9D9C71C2DB24}">
   <dimension ref="A1:M39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="33.6640625" customWidth="1"/>
+    <col min="13" max="13" width="33.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -904,14 +926,14 @@
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>39</v>
+      <c r="F5" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>3</v>
@@ -935,1008 +957,1132 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="12">
         <v>2000</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <v>0.08</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>120000</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <v>240000</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>0.5</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="6">
+      <c r="G6" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="5" t="e">
         <f>0.3*ABS(G6-36.3)/36.3 + 0.25*ABS(H6-2.56)/2.56 + 0.2*ABS(I6-0.37)/0.37 + 0.25*ABS(J6-0.31)/0.31</f>
-        <v>1</v>
-      </c>
-      <c r="L6" s="7" t="s">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="M6" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>2000</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <v>0.08</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>120000</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>240000</v>
       </c>
-      <c r="F7" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="9">
-        <f t="shared" ref="K7:K26" si="0">0.3*ABS(G7-36.3)/36.3 + 0.25*ABS(H7-2.56)/2.56 + 0.2*ABS(I7-0.37)/0.37 + 0.25*ABS(J7-0.31)/0.31</f>
-        <v>1</v>
-      </c>
-      <c r="L7" s="10" t="s">
+      <c r="F7" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="7">
+        <v>71.239999999999995</v>
+      </c>
+      <c r="H7" s="7">
+        <v>1.31</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0.37</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="K7" s="8">
+        <f>0.3*ABS(G7-36.3)/36.3 + 0.25*ABS(H7-2.56)/2.56 + 0.2*ABS(I7-0.37)/0.37 + 0.25*ABS(J7-0.31)/0.31</f>
+        <v>0.55599193340109299</v>
+      </c>
+      <c r="L7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M7" s="16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M7" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>3</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <v>1500</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <v>0.08</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>120000</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <v>240000</v>
       </c>
-      <c r="F8" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L8" s="10" t="s">
+      <c r="F8" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="7">
+        <v>61.06</v>
+      </c>
+      <c r="H8" s="7">
+        <v>1.52</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.37</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.46</v>
+      </c>
+      <c r="K8" s="8">
+        <f t="shared" ref="K7:K26" si="0">0.3*ABS(G8-36.3)/36.3 + 0.25*ABS(H8-2.56)/2.56 + 0.2*ABS(I8-0.37)/0.37 + 0.25*ABS(J8-0.31)/0.31</f>
+        <v>0.42715834110903761</v>
+      </c>
+      <c r="L8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M8" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>4</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="13">
         <v>1200</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="13">
         <v>0.08</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="13">
         <v>120000</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="13">
         <v>240000</v>
       </c>
-      <c r="F9" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="9">
+      <c r="F9" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="10">
+        <v>59.96</v>
+      </c>
+      <c r="H9" s="10">
+        <v>1.63</v>
+      </c>
+      <c r="I9" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="J9" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="K9" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L9" s="10" t="s">
+        <v>0.40466613379450173</v>
+      </c>
+      <c r="L9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="M9" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>5</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="13">
         <v>800</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="13">
         <v>0.08</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <v>120000</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <v>240000</v>
       </c>
-      <c r="F10" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="9">
+      <c r="F10" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G10" s="7">
+        <v>58.14</v>
+      </c>
+      <c r="H10" s="7">
+        <v>1.6</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0.42</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0.43</v>
+      </c>
+      <c r="K10" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L10" s="10" t="s">
+        <v>0.39804708834400915</v>
+      </c>
+      <c r="L10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="M10" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M10" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>6</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>600</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="13">
         <v>0.08</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>120000</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <v>240000</v>
       </c>
-      <c r="F11" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="9">
+      <c r="F11" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="7">
+        <v>57.28</v>
+      </c>
+      <c r="H11" s="7">
+        <v>1.62</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0.47</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0.41</v>
+      </c>
+      <c r="K11" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L11" s="10" t="s">
+        <v>0.39988452009644276</v>
+      </c>
+      <c r="L11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M11" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>7</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="13">
         <v>400</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="13">
         <v>0.08</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>120000</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="13">
         <v>240000</v>
       </c>
-      <c r="F12" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9">
+      <c r="F12" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G12" s="7">
+        <v>58.78</v>
+      </c>
+      <c r="H12" s="7">
+        <v>1.58</v>
+      </c>
+      <c r="I12" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="K12" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L12" s="10" t="s">
+        <v>0.41086924286406512</v>
+      </c>
+      <c r="L12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="M12" s="16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M12" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>8</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>1200</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="13">
         <v>0.08</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <v>80000</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="13">
         <v>160000</v>
       </c>
-      <c r="F13" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="9">
+      <c r="F13" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G13" s="7">
+        <v>63.04</v>
+      </c>
+      <c r="H13" s="7">
+        <v>1.48</v>
+      </c>
+      <c r="I13" s="7">
+        <v>0.37</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="K13" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L13" s="10" t="s">
+        <v>0.43936371134364172</v>
+      </c>
+      <c r="L13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M13" s="16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M13" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>9</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <v>800</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13">
         <v>0.08</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13">
         <v>80000</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="13">
         <v>160000</v>
       </c>
-      <c r="F14" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="9">
+      <c r="F14" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="7">
+        <v>50.78</v>
+      </c>
+      <c r="H14" s="7">
+        <v>1.83</v>
+      </c>
+      <c r="I14" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="J14" s="7">
+        <v>0.41</v>
+      </c>
+      <c r="K14" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L14" s="10" t="s">
+        <v>0.28241445608873672</v>
+      </c>
+      <c r="L14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M14" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>10</v>
       </c>
-      <c r="B15" s="14">
-        <v>600</v>
-      </c>
-      <c r="C15" s="14">
+      <c r="B15" s="13">
+        <v>1500</v>
+      </c>
+      <c r="C15" s="13">
         <v>0.08</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13">
         <v>80000</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="13">
         <v>160000</v>
       </c>
-      <c r="F15" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="9">
+      <c r="F15" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G15" s="10">
+        <v>58.4</v>
+      </c>
+      <c r="H15" s="10">
+        <v>1.59</v>
+      </c>
+      <c r="I15" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="J15" s="10">
+        <v>0.47</v>
+      </c>
+      <c r="K15" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L15" s="10" t="s">
+        <v>0.41180885406909506</v>
+      </c>
+      <c r="L15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M15" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M15" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>11</v>
       </c>
-      <c r="B16" s="14">
-        <v>400</v>
-      </c>
-      <c r="C16" s="14">
+      <c r="B16" s="13">
+        <v>600</v>
+      </c>
+      <c r="C16" s="13">
         <v>0.08</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13">
         <v>80000</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="13">
         <v>160000</v>
       </c>
-      <c r="F16" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="9">
+      <c r="F16" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G16" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="H16" s="7">
+        <v>1.7</v>
+      </c>
+      <c r="I16" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="K16" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L16" s="10" t="s">
+        <v>0.3202683929555723</v>
+      </c>
+      <c r="L16" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="M16" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M16" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>12</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="13">
         <v>1200</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="13">
         <v>0.08</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="13">
         <v>60000</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="13">
         <v>120000</v>
       </c>
-      <c r="F17" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="9">
+      <c r="F17" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G17" s="10">
+        <v>59.3</v>
+      </c>
+      <c r="H17" s="10">
+        <v>1.57</v>
+      </c>
+      <c r="I17" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="J17" s="10">
+        <v>0.44</v>
+      </c>
+      <c r="K17" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L17" s="10" t="s">
+        <v>0.40241185261632939</v>
+      </c>
+      <c r="L17" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M17" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="23">
+      <c r="M17" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
         <v>13</v>
       </c>
-      <c r="B18" s="24">
-        <v>800</v>
-      </c>
-      <c r="C18" s="24">
-        <v>0.08</v>
-      </c>
-      <c r="D18" s="24">
-        <v>60000</v>
-      </c>
-      <c r="E18" s="24">
-        <v>120000</v>
-      </c>
-      <c r="F18" s="24">
-        <v>0.3</v>
-      </c>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="9">
+      <c r="B18" s="18">
+        <v>1200</v>
+      </c>
+      <c r="C18" s="18">
+        <v>0.16</v>
+      </c>
+      <c r="D18" s="18">
+        <v>80000</v>
+      </c>
+      <c r="E18" s="18">
+        <v>160000</v>
+      </c>
+      <c r="F18" s="18">
+        <v>0.3</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="8" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L18" s="26" t="s">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L18" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="M18" s="27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M18" s="21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>14</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="13">
         <v>600</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="13">
         <v>0.08</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="13">
         <v>60000</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="13">
         <v>120000</v>
       </c>
-      <c r="F19" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="9">
+      <c r="F19" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G19" s="3">
+        <v>53.4</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1.74</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="K19" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L19" s="10" t="s">
+        <v>0.30213278429806106</v>
+      </c>
+      <c r="L19" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M19" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M19" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>15</v>
       </c>
-      <c r="B20" s="14">
-        <v>400</v>
-      </c>
-      <c r="C20" s="14">
+      <c r="B20" s="13">
+        <v>1500</v>
+      </c>
+      <c r="C20" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="D20" s="13">
+        <v>60000</v>
+      </c>
+      <c r="E20" s="13">
+        <v>120000</v>
+      </c>
+      <c r="F20" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G20" s="10">
+        <v>40.78</v>
+      </c>
+      <c r="H20" s="10">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="I20" s="10">
+        <v>0.47</v>
+      </c>
+      <c r="J20" s="10">
+        <v>0.41</v>
+      </c>
+      <c r="K20" s="8">
+        <f t="shared" si="0"/>
+        <v>0.19906775873280641</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <v>16</v>
+      </c>
+      <c r="B21" s="18">
+        <v>1200</v>
+      </c>
+      <c r="C21" s="18">
         <v>0.08</v>
       </c>
-      <c r="D20" s="14">
-        <v>60000</v>
-      </c>
-      <c r="E20" s="14">
-        <v>120000</v>
-      </c>
-      <c r="F20" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="9">
+      <c r="D21" s="18">
+        <v>40000</v>
+      </c>
+      <c r="E21" s="18">
+        <v>80000</v>
+      </c>
+      <c r="F21" s="18">
+        <v>0.3</v>
+      </c>
+      <c r="G21" s="19">
+        <v>58.96</v>
+      </c>
+      <c r="H21" s="19">
+        <v>1.58</v>
+      </c>
+      <c r="I21" s="19">
+        <v>0.36</v>
+      </c>
+      <c r="J21" s="19">
+        <v>0.45</v>
+      </c>
+      <c r="K21" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L20" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="M20" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="18">
-        <v>16</v>
-      </c>
-      <c r="B21" s="19">
-        <v>1200</v>
-      </c>
-      <c r="C21" s="19">
-        <v>0.08</v>
-      </c>
-      <c r="D21" s="19">
-        <v>40000</v>
-      </c>
-      <c r="E21" s="19">
-        <v>80000</v>
-      </c>
-      <c r="F21" s="19">
-        <v>0.3</v>
-      </c>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L21" s="21" t="s">
+        <v>0.40128448348458434</v>
+      </c>
+      <c r="L21" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="M21" s="22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M21" s="21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>17</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="13">
         <v>800</v>
       </c>
-      <c r="C22" s="14">
-        <v>0.08</v>
-      </c>
-      <c r="D22" s="14">
-        <v>40000</v>
-      </c>
-      <c r="E22" s="14">
+      <c r="C22" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="D22" s="13">
         <v>80000</v>
       </c>
-      <c r="F22" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="9">
+      <c r="E22" s="13">
+        <v>160000</v>
+      </c>
+      <c r="F22" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G22" s="3">
+        <v>48.18</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1.93</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.59</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="K22" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L22" s="10" t="s">
+        <v>0.33507578750396294</v>
+      </c>
+      <c r="L22" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M22" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>18</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="13">
         <v>600</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13">
         <v>0.08</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13">
         <v>40000</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="13">
         <v>80000</v>
       </c>
-      <c r="F23" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="9">
+      <c r="F23" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G23" s="3">
+        <v>54.64</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="K23" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L23" s="10" t="s">
+        <v>0.33790858980398025</v>
+      </c>
+      <c r="L23" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="M23" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M23" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>19</v>
       </c>
-      <c r="B24" s="14">
-        <v>400</v>
-      </c>
-      <c r="C24" s="14">
-        <v>0.08</v>
-      </c>
-      <c r="D24" s="14">
-        <v>40000</v>
-      </c>
-      <c r="E24" s="14">
-        <v>80000</v>
-      </c>
-      <c r="F24" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="9">
+      <c r="B24" s="13">
+        <v>1200</v>
+      </c>
+      <c r="C24" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="D24" s="13">
+        <v>60000</v>
+      </c>
+      <c r="E24" s="13">
+        <v>120000</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="K24" s="8" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L24" s="10" t="s">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L24" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="M24" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M24" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>20</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="13">
         <v>800</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="13">
         <v>0.08</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="13">
         <v>120000</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="13">
         <v>240000</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="13">
         <v>0.5</v>
       </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="9">
+      <c r="G25" s="3">
+        <v>67.38</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1.38</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="K25" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L25" s="10" t="s">
+        <v>0.49040251034408844</v>
+      </c>
+      <c r="L25" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="M25" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M25" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>21</v>
       </c>
-      <c r="B26" s="14">
-        <v>600</v>
-      </c>
-      <c r="C26" s="14">
+      <c r="B26" s="13">
+        <v>1000</v>
+      </c>
+      <c r="C26" s="13">
         <v>0.08</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="13">
         <v>80000</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="13">
         <v>160000</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="13">
         <v>0.5</v>
       </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="9">
+      <c r="G26" s="3">
+        <v>77.739999999999995</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0.47</v>
+      </c>
+      <c r="K26" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L26" s="10" t="s">
+        <v>0.62594571852911296</v>
+      </c>
+      <c r="L26" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M26" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="28" t="s">
+      <c r="M26" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="28"/>
-    </row>
-    <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="37"/>
+      <c r="M30" s="37"/>
+    </row>
+    <row r="32" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>22</v>
       </c>
-      <c r="B32" s="14">
-        <v>800</v>
-      </c>
-      <c r="C32" s="14">
-        <v>0.06</v>
-      </c>
-      <c r="D32" s="14">
+      <c r="B32" s="13">
+        <v>1500</v>
+      </c>
+      <c r="C32" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="D32" s="13">
         <v>60000</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="13">
         <v>120000</v>
       </c>
-      <c r="F32" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="9">
+      <c r="F32" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G32" s="3">
+        <v>49.54</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1.88</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0.42</v>
+      </c>
+      <c r="K32" s="8">
         <f>0.3*ABS(G32-36.3)/36.3 + 0.25*ABS(H32-2.56)/2.56 + 0.2*ABS(I32-0.37)/0.37 + 0.25*ABS(J32-0.31)/0.31</f>
-        <v>1</v>
-      </c>
-      <c r="L32" s="10" t="s">
+        <v>0.28615903664428227</v>
+      </c>
+      <c r="L32" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="M32" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M32" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>23</v>
       </c>
-      <c r="B33" s="14">
-        <v>800</v>
-      </c>
-      <c r="C33" s="14">
+      <c r="B33" s="13">
+        <v>1500</v>
+      </c>
+      <c r="C33" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="D33" s="13">
+        <v>40000</v>
+      </c>
+      <c r="E33" s="13">
+        <v>80000</v>
+      </c>
+      <c r="F33" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G33" s="3">
+        <v>42.96</v>
+      </c>
+      <c r="H33" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0.47</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="K33" s="8">
+        <f t="shared" ref="K33:K35" si="1">0.3*ABS(G33-36.3)/36.3 + 0.25*ABS(H33-2.56)/2.56 + 0.2*ABS(I33-0.37)/0.37 + 0.25*ABS(J33-0.31)/0.31</f>
+        <v>0.22880303765842624</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="17">
+        <v>24</v>
+      </c>
+      <c r="B34" s="18">
+        <v>1200</v>
+      </c>
+      <c r="C34" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="D34" s="18">
+        <v>60000</v>
+      </c>
+      <c r="E34" s="18">
+        <v>120000</v>
+      </c>
+      <c r="F34" s="18">
+        <v>0.3</v>
+      </c>
+      <c r="G34" s="19">
+        <v>49.6</v>
+      </c>
+      <c r="H34" s="19">
+        <v>1.88</v>
+      </c>
+      <c r="I34" s="19">
+        <v>0.39</v>
+      </c>
+      <c r="J34" s="19">
+        <v>0.41</v>
+      </c>
+      <c r="K34" s="8">
+        <f t="shared" si="1"/>
+        <v>0.26777957747303427</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="M34" s="21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="31">
+        <v>25</v>
+      </c>
+      <c r="B35" s="32">
+        <v>1200</v>
+      </c>
+      <c r="C35" s="32">
         <v>0.06</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D35" s="32">
         <v>40000</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E35" s="32">
         <v>80000</v>
       </c>
-      <c r="F33" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="9">
-        <f t="shared" ref="K33:K39" si="1">0.3*ABS(G33-36.3)/36.3 + 0.25*ABS(H33-2.56)/2.56 + 0.2*ABS(I33-0.37)/0.37 + 0.25*ABS(J33-0.31)/0.31</f>
-        <v>1</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M33" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="23">
-        <v>24</v>
-      </c>
-      <c r="B34" s="24">
-        <v>800</v>
-      </c>
-      <c r="C34" s="24">
-        <v>0.04</v>
-      </c>
-      <c r="D34" s="24">
-        <v>60000</v>
-      </c>
-      <c r="E34" s="24">
-        <v>120000</v>
-      </c>
-      <c r="F34" s="24">
-        <v>0.3</v>
-      </c>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="9">
+      <c r="F35" s="32">
+        <v>0.3</v>
+      </c>
+      <c r="G35" s="33">
+        <v>46.68</v>
+      </c>
+      <c r="H35" s="33">
+        <v>1.99</v>
+      </c>
+      <c r="I35" s="33">
+        <v>0.4</v>
+      </c>
+      <c r="J35" s="33">
+        <v>0.42</v>
+      </c>
+      <c r="K35" s="34">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L34" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="M34" s="27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>25</v>
-      </c>
-      <c r="B35" s="14">
-        <v>800</v>
-      </c>
-      <c r="C35" s="14">
-        <v>0.04</v>
-      </c>
-      <c r="D35" s="14">
-        <v>40000</v>
-      </c>
-      <c r="E35" s="14">
-        <v>80000</v>
-      </c>
-      <c r="F35" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L35" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="M35" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>26</v>
-      </c>
-      <c r="B36" s="14">
-        <v>800</v>
-      </c>
-      <c r="C36" s="14">
-        <v>0.06</v>
-      </c>
-      <c r="D36" s="14">
-        <v>50000</v>
-      </c>
-      <c r="E36" s="14">
-        <v>100000</v>
-      </c>
-      <c r="F36" s="14">
-        <v>0.25</v>
-      </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L36" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="M36" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
-        <v>27</v>
-      </c>
-      <c r="B37" s="14">
-        <v>800</v>
-      </c>
-      <c r="C37" s="14">
-        <v>0.02</v>
-      </c>
-      <c r="D37" s="14">
-        <v>60000</v>
-      </c>
-      <c r="E37" s="14">
-        <v>120000</v>
-      </c>
-      <c r="F37" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L37" s="10" t="s">
+        <v>0.24637508010251324</v>
+      </c>
+      <c r="L35" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="M35" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="M37" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
-        <v>28</v>
-      </c>
-      <c r="B38" s="14">
-        <v>1000</v>
-      </c>
-      <c r="C38" s="14">
-        <v>0.04</v>
-      </c>
-      <c r="D38" s="14">
-        <v>60000</v>
-      </c>
-      <c r="E38" s="14">
-        <v>120000</v>
-      </c>
-      <c r="F38" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L38" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="M38" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
-        <v>29</v>
-      </c>
-      <c r="B39" s="14">
-        <v>1000</v>
-      </c>
-      <c r="C39" s="14">
-        <v>0.02</v>
-      </c>
-      <c r="D39" s="14">
-        <v>60000</v>
-      </c>
-      <c r="E39" s="14">
-        <v>120000</v>
-      </c>
-      <c r="F39" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L39" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="M39" s="17" t="s">
-        <v>71</v>
-      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="25"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="29"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="25"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="29"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="25"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="29"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="25"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="27"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="4">
